--- a/docs/verification/files/rocscience_gw/gw006d.xlsx
+++ b/docs/verification/files/rocscience_gw/gw006d.xlsx
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="I3" s="33">
-        <v>8.9e-09</v>
+        <v>8.94427191e-09</v>
       </c>
       <c r="K3" s="32" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="O3" s="33">
-        <v>8.9e-09</v>
+        <v>8.94427191e-09</v>
       </c>
       <c r="Q3" s="32" t="inlineStr">
         <is>
